--- a/filer/47458714_lego.xlsx
+++ b/filer/47458714_lego.xlsx
@@ -182,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -252,15 +252,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5250,7 +5241,9 @@
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="16" t="n"/>
       <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
+      <c r="E14" s="16" t="n">
+        <v>175000</v>
+      </c>
       <c r="F14" s="16" t="n">
         <v>10187000</v>
       </c>
@@ -7275,7 +7268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7372,37 +7365,6 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B4" s="37" t="inlineStr">
-        <is>
-          <t>fsa:OtherInvestmentAssets</t>
-        </is>
-      </c>
-      <c r="C4" s="37" t="inlineStr">
-        <is>
-          <t>fsa:OtherInvestmentAssets</t>
-        </is>
-      </c>
-      <c r="D4" s="38" t="n"/>
-      <c r="E4" s="38" t="n"/>
-      <c r="F4" s="38" t="n"/>
-      <c r="G4" s="38" t="n">
-        <v>175000</v>
-      </c>
-      <c r="H4" s="38" t="n">
-        <v>202000</v>
-      </c>
-      <c r="I4" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filer/47458714_lego.xlsx
+++ b/filer/47458714_lego.xlsx
@@ -639,7 +639,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/47458714_lego.xlsx
+++ b/filer/47458714_lego.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -653,7 +653,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -668,35 +668,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1426,35 +1426,35 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
@@ -2760,35 +2760,35 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
@@ -4142,19 +4142,19 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
@@ -4260,19 +4260,19 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
@@ -4570,6 +4570,13 @@
       <c r="F94" s="13">
         <f>IFERROR($F$34/($F$56+$F$63)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4601,19 +4608,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4623,19 +4630,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>31499000</v>
+        <v>40925000</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>40925000</v>
+        <v>48295000</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>48295000</v>
+        <v>47957000</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>47957000</v>
+        <v>55590000</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>55590000</v>
+        <v>61963000</v>
       </c>
     </row>
     <row r="3">
@@ -4645,19 +4652,19 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>14136000</v>
+        <v>17545000</v>
       </c>
       <c r="C3" s="16" t="n">
-        <v>17545000</v>
+        <v>21641000</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>21641000</v>
+        <v>22828000</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>22828000</v>
+        <v>26075000</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>26075000</v>
+        <v>29937000</v>
       </c>
     </row>
     <row r="4">
@@ -4667,19 +4674,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>17363000</v>
+        <v>23380000</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>23380000</v>
+        <v>26654000</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>26654000</v>
+        <v>25129000</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>25129000</v>
+        <v>29515000</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>29515000</v>
+        <v>32026000</v>
       </c>
     </row>
     <row r="5">
@@ -4689,19 +4696,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>4799000</v>
+        <v>6266000</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>6266000</v>
+        <v>7592000</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>7592000</v>
+        <v>7616000</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>7616000</v>
+        <v>8884000</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>8884000</v>
+        <v>9544000</v>
       </c>
     </row>
     <row r="6">
@@ -4711,19 +4718,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>2065000</v>
+        <v>2657000</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>2657000</v>
+        <v>2746000</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>2746000</v>
+        <v>3187000</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>3187000</v>
+        <v>3884000</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>3884000</v>
+        <v>4157000</v>
       </c>
     </row>
     <row r="7">
@@ -4745,19 +4752,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>1015000</v>
+        <v>999000</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>999000</v>
+        <v>1594000</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1594000</v>
+        <v>1876000</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>1876000</v>
+        <v>2447000</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>2447000</v>
+        <v>2544000</v>
       </c>
     </row>
     <row r="9">
@@ -4767,19 +4774,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>10499000</v>
+        <v>14457000</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>14457000</v>
+        <v>16316000</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>16316000</v>
+        <v>14326000</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>14326000</v>
+        <v>16747000</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>16747000</v>
+        <v>18325000</v>
       </c>
     </row>
     <row r="10">
@@ -4801,19 +4808,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>309000</v>
+        <v>382000</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>382000</v>
+        <v>587000</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>587000</v>
+        <v>1690000</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>1690000</v>
+        <v>1296000</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>1296000</v>
+        <v>1410000</v>
       </c>
     </row>
     <row r="12">
@@ -4823,19 +4830,19 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>375000</v>
+        <v>186000</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>186000</v>
+        <v>990000</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>990000</v>
+        <v>377000</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>377000</v>
+        <v>948000</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>948000</v>
+        <v>242000</v>
       </c>
     </row>
     <row r="13">
@@ -4845,19 +4852,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>-66000</v>
+        <v>196000</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>196000</v>
+        <v>-403000</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-403000</v>
+        <v>1313000</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>1313000</v>
+        <v>348000</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>348000</v>
+        <v>1168000</v>
       </c>
     </row>
     <row r="14">
@@ -4867,19 +4874,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>9418000</v>
+        <v>13654000</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>13654000</v>
+        <v>14319000</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>14319000</v>
+        <v>13763000</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>13763000</v>
+        <v>14648000</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>14648000</v>
+        <v>16949000</v>
       </c>
     </row>
     <row r="15">
@@ -4889,19 +4896,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>2132000</v>
+        <v>2981000</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>2981000</v>
+        <v>2949000</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>2949000</v>
+        <v>2851000</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>2851000</v>
+        <v>3243000</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>3243000</v>
+        <v>3691000</v>
       </c>
     </row>
     <row r="16">
@@ -4911,19 +4918,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>7286000</v>
+        <v>10673000</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>10673000</v>
+        <v>11370000</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>11370000</v>
+        <v>10912000</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>10912000</v>
+        <v>11405000</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>11405000</v>
+        <v>13258000</v>
       </c>
     </row>
     <row r="17">
@@ -4933,19 +4940,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>4</v>
+        <v>4409</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>4409</v>
+        <v>4958</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>4958</v>
+        <v>5587</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>5587</v>
+        <v>5950</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>5950</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="18">
@@ -4955,19 +4962,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>909000</v>
+        <v>1313000</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>1313000</v>
+        <v>1822000</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>1822000</v>
+        <v>1707000</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>1707000</v>
+        <v>1900000</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>1900000</v>
+        <v>2528000</v>
       </c>
     </row>
   </sheetData>
@@ -4999,19 +5006,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -5021,19 +5028,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>35000</v>
+        <v>51000</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>51000</v>
+        <v>126000</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>126000</v>
+        <v>306000</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>306000</v>
+        <v>442000</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>442000</v>
+        <v>629000</v>
       </c>
     </row>
     <row r="3">
@@ -5067,19 +5074,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>112000</v>
+        <v>81000</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>81000</v>
+        <v>143000</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>143000</v>
+        <v>310000</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>310000</v>
+        <v>445000</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>445000</v>
+        <v>631000</v>
       </c>
     </row>
     <row r="6">
@@ -5089,19 +5096,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>620000</v>
+        <v>563000</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>563000</v>
+        <v>589000</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>589000</v>
+        <v>573000</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>573000</v>
+        <v>556000</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>556000</v>
+        <v>672000</v>
       </c>
     </row>
     <row r="7">
@@ -5111,19 +5118,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>1839000</v>
+        <v>2061000</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>2061000</v>
+        <v>2283000</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>2283000</v>
+        <v>2419000</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>2419000</v>
+        <v>2307000</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>2307000</v>
+        <v>3357000</v>
       </c>
     </row>
     <row r="8">
@@ -5133,19 +5140,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>186000</v>
+        <v>209000</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>209000</v>
+        <v>293000</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>293000</v>
+        <v>306000</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>306000</v>
+        <v>336000</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>336000</v>
+        <v>286000</v>
       </c>
     </row>
     <row r="9">
@@ -5167,19 +5174,19 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>393000</v>
+        <v>645000</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>645000</v>
+        <v>1246000</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1246000</v>
+        <v>1782000</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>1782000</v>
+        <v>2849000</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>2849000</v>
+        <v>3431000</v>
       </c>
     </row>
     <row r="11">
@@ -5189,19 +5196,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>3038000</v>
+        <v>3478000</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>3478000</v>
+        <v>4411000</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>4411000</v>
+        <v>5080000</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5080000</v>
+        <v>6048000</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>6048000</v>
+        <v>7746000</v>
       </c>
     </row>
     <row r="12">
@@ -5224,12 +5231,14 @@
       </c>
       <c r="B13" s="16" t="n"/>
       <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
+      <c r="D13" s="16" t="n">
+        <v>5098000</v>
+      </c>
       <c r="E13" s="16" t="n">
-        <v>5098000</v>
+        <v>10077000</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>10077000</v>
+        <v>9475000</v>
       </c>
     </row>
     <row r="14">
@@ -5240,12 +5249,14 @@
       </c>
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
+      <c r="D14" s="16" t="n">
+        <v>175000</v>
+      </c>
       <c r="E14" s="16" t="n">
-        <v>175000</v>
+        <v>10187000</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>10187000</v>
+        <v>9703000</v>
       </c>
     </row>
     <row r="15">
@@ -5255,19 +5266,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>4274000</v>
+        <v>5552000</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>5552000</v>
+        <v>6556000</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>6556000</v>
+        <v>12503000</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>12503000</v>
+        <v>18893000</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>18893000</v>
+        <v>20827000</v>
       </c>
     </row>
     <row r="16">
@@ -5277,19 +5288,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>1786000</v>
+        <v>2126000</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>2126000</v>
+        <v>3522000</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3522000</v>
+        <v>3378000</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>3378000</v>
+        <v>4034000</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>4034000</v>
+        <v>4505000</v>
       </c>
     </row>
     <row r="17">
@@ -5299,19 +5310,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>620000</v>
+        <v>622000</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>622000</v>
+        <v>399000</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>399000</v>
+        <v>421000</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>421000</v>
+        <v>517000</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>517000</v>
+        <v>537000</v>
       </c>
     </row>
     <row r="18">
@@ -5321,19 +5332,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>24616000</v>
+        <v>27394000</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>27394000</v>
+        <v>28959000</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>28959000</v>
+        <v>23782000</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>23782000</v>
+        <v>21833000</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>21833000</v>
+        <v>23125000</v>
       </c>
     </row>
     <row r="19">
@@ -5343,19 +5354,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>671000</v>
+        <v>818000</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>818000</v>
+        <v>1391000</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>1391000</v>
+        <v>1438000</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>1438000</v>
+        <v>771000</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>771000</v>
+        <v>1130000</v>
       </c>
     </row>
     <row r="20">
@@ -5365,10 +5376,10 @@
         </is>
       </c>
       <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="D20" s="16" t="n"/>
       <c r="E20" s="16" t="n"/>
       <c r="F20" s="16" t="n"/>
     </row>
@@ -5378,16 +5389,18 @@
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n">
+      <c r="B21" s="16" t="n">
         <v>66000</v>
       </c>
-      <c r="D21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n">
+        <v>39000</v>
+      </c>
       <c r="E21" s="16" t="n">
-        <v>39000</v>
+        <v>79000</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>79000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -5409,14 +5422,14 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>140000</v>
-      </c>
-      <c r="C23" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n">
+        <v>531000</v>
+      </c>
       <c r="E23" s="16" t="n">
-        <v>531000</v>
+        <v>501000</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>501000</v>
@@ -5429,19 +5442,19 @@
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>26047000</v>
+        <v>28900000</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>28900000</v>
+        <v>30749000</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>30749000</v>
+        <v>26211000</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>26211000</v>
+        <v>24085000</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>24085000</v>
+        <v>25720000</v>
       </c>
     </row>
     <row r="25">
@@ -5463,19 +5476,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>500000</v>
+        <v>427000</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>427000</v>
+        <v>509000</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>509000</v>
+        <v>102000</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>102000</v>
+        <v>0</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>0</v>
+        <v>185000</v>
       </c>
     </row>
     <row r="27">
@@ -5485,19 +5498,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>28333000</v>
+        <v>31453000</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>31453000</v>
+        <v>34780000</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>34780000</v>
+        <v>29691000</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>29691000</v>
+        <v>28119000</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>28119000</v>
+        <v>30410000</v>
       </c>
     </row>
     <row r="28">
@@ -5507,19 +5520,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>32607000</v>
+        <v>37005000</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>37005000</v>
+        <v>41336000</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>41336000</v>
+        <v>42194000</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>42194000</v>
+        <v>47012000</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>47012000</v>
+        <v>51237000</v>
       </c>
     </row>
     <row r="29">
@@ -5563,19 +5576,19 @@
         </is>
       </c>
       <c r="B31" s="16" t="n">
-        <v>76000</v>
+        <v>63000</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>63000</v>
+        <v>112000</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>112000</v>
+        <v>242000</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>242000</v>
+        <v>347000</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>347000</v>
+        <v>493000</v>
       </c>
     </row>
     <row r="32">
@@ -5584,18 +5597,20 @@
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
+      <c r="B32" s="16" t="n">
+        <v>-161000</v>
+      </c>
       <c r="C32" s="16" t="n">
-        <v>-161000</v>
+        <v>157000</v>
       </c>
       <c r="D32" s="16" t="n">
-        <v>157000</v>
+        <v>54000</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>54000</v>
+        <v>-216000</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>-216000</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="33">
@@ -5604,9 +5619,7 @@
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
-        <v>91000</v>
-      </c>
+      <c r="B33" s="16" t="n"/>
       <c r="C33" s="16" t="n"/>
       <c r="D33" s="16" t="n"/>
       <c r="E33" s="16" t="n"/>
@@ -5619,19 +5632,19 @@
         </is>
       </c>
       <c r="B34" s="16" t="n">
-        <v>5984000</v>
+        <v>6670000</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>6670000</v>
+        <v>8991000</v>
       </c>
       <c r="D34" s="16" t="n">
-        <v>8991000</v>
+        <v>10773000</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>10773000</v>
+        <v>13073000</v>
       </c>
       <c r="F34" s="16" t="n">
-        <v>13073000</v>
+        <v>12185000</v>
       </c>
     </row>
     <row r="35">
@@ -5641,19 +5654,19 @@
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>14201000</v>
+        <v>16622000</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>16622000</v>
+        <v>18310000</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>18310000</v>
+        <v>20119000</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>20119000</v>
+        <v>22254000</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>22254000</v>
+        <v>24875000</v>
       </c>
     </row>
     <row r="36">
@@ -5663,18 +5676,18 @@
         </is>
       </c>
       <c r="B36" s="16" t="n">
-        <v>83000</v>
+        <v>0</v>
       </c>
       <c r="C36" s="16" t="n">
+        <v>26000</v>
+      </c>
+      <c r="D36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="16" t="n">
-        <v>26000</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n">
+        <v>81000</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -5683,19 +5696,19 @@
         </is>
       </c>
       <c r="B37" s="16" t="n">
-        <v>105000</v>
+        <v>46000</v>
       </c>
       <c r="C37" s="16" t="n">
-        <v>46000</v>
+        <v>100000</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>100000</v>
+        <v>24000</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>24000</v>
+        <v>9000</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>9000</v>
+        <v>89000</v>
       </c>
     </row>
     <row r="38">
@@ -5717,17 +5730,15 @@
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>137000</v>
+        <v>127000</v>
       </c>
       <c r="C39" s="16" t="n">
-        <v>127000</v>
+        <v>118000</v>
       </c>
       <c r="D39" s="16" t="n">
-        <v>118000</v>
-      </c>
-      <c r="E39" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="E39" s="16" t="n"/>
       <c r="F39" s="16" t="n"/>
     </row>
     <row r="40">
@@ -5737,19 +5748,19 @@
         </is>
       </c>
       <c r="B40" s="16" t="n">
-        <v>991000</v>
+        <v>1838000</v>
       </c>
       <c r="C40" s="16" t="n">
-        <v>1838000</v>
+        <v>1827000</v>
       </c>
       <c r="D40" s="16" t="n">
-        <v>1827000</v>
+        <v>1860000</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>1860000</v>
+        <v>1982000</v>
       </c>
       <c r="F40" s="16" t="n">
-        <v>1982000</v>
+        <v>2558000</v>
       </c>
     </row>
     <row r="41">
@@ -5758,17 +5769,17 @@
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="16" t="n">
+        <v>95000</v>
+      </c>
+      <c r="D41" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n">
-        <v>95000</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="16" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="16" t="n">
+        <v>97000</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
@@ -5777,19 +5788,19 @@
         </is>
       </c>
       <c r="B42" s="16" t="n">
-        <v>1151000</v>
+        <v>1965000</v>
       </c>
       <c r="C42" s="16" t="n">
-        <v>1965000</v>
+        <v>2040000</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>2040000</v>
+        <v>1860000</v>
       </c>
       <c r="E42" s="16" t="n">
-        <v>1860000</v>
+        <v>1982000</v>
       </c>
       <c r="F42" s="16" t="n">
-        <v>1982000</v>
+        <v>2655000</v>
       </c>
     </row>
     <row r="43">
@@ -5826,16 +5837,16 @@
         <v>10000</v>
       </c>
       <c r="C45" s="16" t="n">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="D45" s="16" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="E45" s="16" t="n">
+        <v>68000</v>
+      </c>
+      <c r="F45" s="16" t="n">
         <v>0</v>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>68000</v>
       </c>
     </row>
     <row r="46">
@@ -5845,19 +5856,19 @@
         </is>
       </c>
       <c r="B46" s="16" t="n">
-        <v>151000</v>
+        <v>181000</v>
       </c>
       <c r="C46" s="16" t="n">
-        <v>181000</v>
+        <v>210000</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>210000</v>
+        <v>202000</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>202000</v>
+        <v>289000</v>
       </c>
       <c r="F46" s="16" t="n">
-        <v>289000</v>
+        <v>249000</v>
       </c>
     </row>
     <row r="47">
@@ -5867,19 +5878,19 @@
         </is>
       </c>
       <c r="B47" s="16" t="n">
-        <v>836000</v>
+        <v>2200000</v>
       </c>
       <c r="C47" s="16" t="n">
-        <v>2200000</v>
+        <v>2408000</v>
       </c>
       <c r="D47" s="16" t="n">
-        <v>2408000</v>
+        <v>2193000</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>2193000</v>
+        <v>2366000</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>2366000</v>
+        <v>2938000</v>
       </c>
     </row>
     <row r="48">
@@ -5889,19 +5900,19 @@
         </is>
       </c>
       <c r="B48" s="16" t="n">
-        <v>13127000</v>
+        <v>12693000</v>
       </c>
       <c r="C48" s="16" t="n">
-        <v>12693000</v>
+        <v>14665000</v>
       </c>
       <c r="D48" s="16" t="n">
-        <v>14665000</v>
+        <v>13495000</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>13495000</v>
+        <v>14038000</v>
       </c>
       <c r="F48" s="16" t="n">
-        <v>14038000</v>
+        <v>13986000</v>
       </c>
     </row>
     <row r="49">
@@ -5922,18 +5933,20 @@
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n"/>
+      <c r="B50" s="16" t="n">
+        <v>18000</v>
+      </c>
       <c r="C50" s="16" t="n">
-        <v>18000</v>
+        <v>232000</v>
       </c>
       <c r="D50" s="16" t="n">
-        <v>232000</v>
+        <v>690000</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>690000</v>
+        <v>561000</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>561000</v>
+        <v>837000</v>
       </c>
     </row>
     <row r="51">
@@ -5955,19 +5968,19 @@
         </is>
       </c>
       <c r="B52" s="16" t="n">
-        <v>2772000</v>
+        <v>2875000</v>
       </c>
       <c r="C52" s="16" t="n">
-        <v>2875000</v>
+        <v>2747000</v>
       </c>
       <c r="D52" s="16" t="n">
-        <v>2747000</v>
+        <v>2803000</v>
       </c>
       <c r="E52" s="16" t="n">
-        <v>2803000</v>
+        <v>4497000</v>
       </c>
       <c r="F52" s="16" t="n">
-        <v>4497000</v>
+        <v>4595000</v>
       </c>
     </row>
     <row r="53">
@@ -5977,19 +5990,19 @@
         </is>
       </c>
       <c r="B53" s="16" t="n">
-        <v>254000</v>
+        <v>395000</v>
       </c>
       <c r="C53" s="16" t="n">
-        <v>395000</v>
+        <v>615000</v>
       </c>
       <c r="D53" s="16" t="n">
-        <v>615000</v>
+        <v>808000</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>808000</v>
+        <v>948000</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>948000</v>
+        <v>1013000</v>
       </c>
     </row>
     <row r="54">
@@ -5999,19 +6012,19 @@
         </is>
       </c>
       <c r="B54" s="16" t="n">
-        <v>17150000</v>
+        <v>18372000</v>
       </c>
       <c r="C54" s="16" t="n">
-        <v>18372000</v>
+        <v>20886000</v>
       </c>
       <c r="D54" s="16" t="n">
-        <v>20886000</v>
+        <v>20191000</v>
       </c>
       <c r="E54" s="16" t="n">
-        <v>20191000</v>
+        <v>22767000</v>
       </c>
       <c r="F54" s="16" t="n">
-        <v>22767000</v>
+        <v>23618000</v>
       </c>
     </row>
     <row r="55">
@@ -6021,19 +6034,19 @@
         </is>
       </c>
       <c r="B55" s="16" t="n">
-        <v>18301000</v>
+        <v>20337000</v>
       </c>
       <c r="C55" s="16" t="n">
-        <v>20337000</v>
+        <v>22926000</v>
       </c>
       <c r="D55" s="16" t="n">
-        <v>22926000</v>
+        <v>22051000</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>22051000</v>
+        <v>24749000</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>24749000</v>
+        <v>26273000</v>
       </c>
     </row>
     <row r="56">
@@ -6043,19 +6056,19 @@
         </is>
       </c>
       <c r="B56" s="16" t="n">
-        <v>32607000</v>
+        <v>37005000</v>
       </c>
       <c r="C56" s="16" t="n">
-        <v>37005000</v>
+        <v>41336000</v>
       </c>
       <c r="D56" s="16" t="n">
-        <v>41336000</v>
+        <v>42194000</v>
       </c>
       <c r="E56" s="16" t="n">
-        <v>42194000</v>
+        <v>47012000</v>
       </c>
       <c r="F56" s="16" t="n">
-        <v>47012000</v>
+        <v>51237000</v>
       </c>
     </row>
   </sheetData>
@@ -6094,13 +6107,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6790,7 +6803,7 @@
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -6908,7 +6921,7 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -7084,7 +7097,7 @@
     <row r="57">
       <c r="A57" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B57" s="29" t="n"/>
@@ -7307,27 +7320,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7352,9 +7365,7 @@
           <t>fsa:LongtermDeferredIncome</t>
         </is>
       </c>
-      <c r="D3" s="35" t="n">
-        <v>23000</v>
-      </c>
+      <c r="D3" s="35" t="n"/>
       <c r="E3" s="35" t="n"/>
       <c r="F3" s="35" t="n"/>
       <c r="G3" s="35" t="n"/>
